--- a/data/describe/few_shot/few_shot_QandA.xlsx
+++ b/data/describe/few_shot/few_shot_QandA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8">
   <si>
     <t>User</t>
   </si>
@@ -19,20 +19,28 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>The name of the factor is: introverted vs extraverted. 
-It was based on the following description of a person: The factor is very strongly positively associated with the feature that they feel comfortable around people, strongly positively associated with the feature that they talk to a lot of different people at parties, strongly positively associated with the feature that they start conversations, strongly positively associated with the feature that they are the life of the party, moderately positively associated with the feature that they interested in people. The factor is strongly negatively associated with the feature that they are quiet around strangers, strongly negatively associated with the feature that they keep in the background, strongly negatively associated with the feature that they not really interested in others, strongly negatively associated with the feature that they have little to say, moderately negatively associated with the feature that they dont talk a lot. 
-Now tell me, what does it mean when an entity is described as extraverted?</t>
+    <t>The name of the factor is: considerate vs carefree. 
+It was based on the following description: The first features we look at should primarily be used to name considerate. The higher the value of the association, the more important the feature is for naming considerate. Here is a list of the features and how important they are for naming considerate: the feature that they get chores done right away is moderately associated with considerate , the feature that they dont like to draw attention to themself is moderately associated with considerate , the feature that they take time out for others is weakly associated with considerate , the feature that they pay attention to details is weakly associated with considerate , the feature that they are always prepared is weakly associated with considerate . The next features we look at should primarily be used to name carefree. The higher the value of the association, the more important the feature is for naming carefree. Here is a list of the features and how important they are for naming carefree: the feature that they insult people is moderately associated with carefree , the feature that they often forget to put things back in their proper place is weakly associated with carefree , the feature that they are the life of the party is weakly associated with carefree , the feature that they leave their belongings around is weakly associated with carefree , the feature that they shirk their duties is weakly associated with carefree .
+Now tell me, what does it mean when a person is described as carefree?</t>
   </si>
   <si>
-    <t>An extraverted person is a social butterfly: effortlessly starting and engaging in conversations at parties and exuding confidence around others. This is a stark contrast to introverted individuals, who like to stay in the background, saying very little and having no desire to engage in constant chatter.</t>
+    <t>Carefree people can occasionally insult others without thinking, they are known to leave their belongings scattered around, and can shirk their duties. On the other hand, being carefree means a person quite likes partying and doesn’t mind being the centre of attention.</t>
   </si>
   <si>
-    <t>The name of the factor is: engaged vs detached. 
-It was based on the following description: The factor is very strongly positively associated with the feature that Are you an active member, inactive member, or not a member of a sport or recreational organization?, very strongly positively associated with the feature that Are you an active member, inactive member, or not a member of another type of organization?, strongly positively associated with the feature that Are you an active member, inactive member, or not a member of an art, music, or educational organization?, strongly positively associated with the feature that Are you an active member, inactive member, or not a member of a consumer organization?, strongly positively associated with the feature that Are you an active member, inactive member, or not a member of a labor union?. The factor is very strongly negatively associated with the feature that How frequently does alcohol consumption in the streets occur in your neighborhood?, very strongly negatively associated with the feature that Please tell me for the following statement how essential you think it is as a characteristic of democracy: Governments tax the rich and subsidize the poor., very strongly negatively associated with the feature that Have you been the victim of a crime during the past year?, strongly negatively associated with the feature that Has someone in your immediate family been the victim of a crime during the past year?, strongly negatively associated with the feature that Do you agree that science and technology will provide more opportunities for the next generation?. 
-Now tell me, what does it mean when a country is described as detached?</t>
+    <t>The name of the factor is: concerned vs untroubled. 
+It was based on the following description: The first features we look at should primarily be used to name concerned. The higher the value of the association, the more important the feature is for naming concerned. Here is a list of the features and how important they are for naming concerned: the feature that they worry about things is strongly associated with concerned , the feature that they have a vivid imagination is moderately associated with concerned , the feature that they get upset easily is moderately associated with concerned , the feature that they change their mood a lot is moderately associated with concerned , the feature that they have excellent ideas is moderately associated with concerned . There are no features used to name untroubled. You should describe it simply as the opposite of concerned, which you already got information about. If possible use a negation such as 'not x' to name untroubled. 
+Now tell me, what does it mean when a person is described as untroubled?</t>
   </si>
   <si>
-    <t>The citizens of a country can be described as detached when they or their families experience crime and/or they feel that neither science or government help them. They are unlike the citizens of countries who are more engaged in community life and become members of sporting and political organisations.</t>
+    <t>An untroubled person doesn’t worry or get easily upset. While they might not have as vivid imagination as more concerned individuals, they are not burdened by worries.</t>
+  </si>
+  <si>
+    <t>The name of the factor is: inactive vs active. 
+It was based on the following description: There are no features primarily be used to name inactive. You should describe it simply as the opposite of active, which we now give more information about in order to choose a name. If possibble use a negation to name inactive. The next features we look at should primarily be used to name active. The higher the value of the association, the more important the feature is for naming active. Here is a list of the features and how important they are for naming active: the feature that assits adjusted per 90 minutes is very strongly associated with active .
+Now tell me, what does it mean when a football player is described as active?</t>
+  </si>
+  <si>
+    <t>In this case active simply refers to a player who makes lots of assists and nothing else.</t>
   </si>
 </sst>
 </file>
@@ -73,7 +81,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="10"/>
+        <fgColor indexed="9"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -88,16 +96,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -114,16 +122,16 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -146,8 +154,8 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ffffffff"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -346,17 +354,17 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -383,10 +391,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -625,12 +633,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -907,7 +915,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -934,10 +942,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1199,7 +1207,7 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" ht="195.75" customHeight="1">
+    <row r="2" ht="236.1" customHeight="1">
       <c r="A2" t="s" s="4">
         <v>2</v>
       </c>
@@ -1211,40 +1219,44 @@
       <c r="E2" s="3"/>
     </row>
     <row r="3" ht="299.55" customHeight="1">
-      <c r="A3" t="s" s="5">
+      <c r="A3" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="B3" t="s" s="5">
+      <c r="B3" t="s" s="2">
         <v>5</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" ht="71.5" customHeight="1">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+    <row r="4" ht="174.5" customHeight="1">
+      <c r="A4" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
     </row>
     <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -1257,15 +1269,15 @@
       <c r="E8" s="3"/>
     </row>
     <row r="9" ht="13.55" customHeight="1">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
     <row r="10" ht="13.55" customHeight="1">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
